--- a/SeleniumTests/TestDataFolder/SettingOnDashboardTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/SettingOnDashboardTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC20B50-C026-4B2C-B310-22747A1151C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AB20CB-1178-434F-9AAB-C0B6CB472382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29235" yWindow="3345" windowWidth="13830" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SettingTestData" sheetId="3" r:id="rId1"/>
@@ -26,29 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>CutOffDate</t>
-  </si>
-  <si>
-    <t>ConsolidateCutOffDate</t>
-  </si>
-  <si>
-    <t>SecurityToken</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>CutOffDateReset</t>
-  </si>
-  <si>
-    <t>ConsolidateCutOffDateReset</t>
-  </si>
-  <si>
-    <t>SecurityTokenReset</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -56,6 +38,27 @@
   </si>
   <si>
     <t>compact</t>
+  </si>
+  <si>
+    <t>B2C Cut Off Date</t>
+  </si>
+  <si>
+    <t>Auto Consolidate Cut Off Date</t>
+  </si>
+  <si>
+    <t>Security Token</t>
+  </si>
+  <si>
+    <t>B2C Cut Off Date Reset</t>
+  </si>
+  <si>
+    <t>Auto Consolidate Cut Off Date Reset</t>
+  </si>
+  <si>
+    <t>Security Token Reset</t>
+  </si>
+  <si>
+    <t>comfortable</t>
   </si>
 </sst>
 </file>
@@ -376,19 +379,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719B516A-664C-4C4D-B673-B11EE392F7B6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -399,10 +408,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -412,21 +421,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3D1677-BF21-4822-B71F-966EBCA0782B}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3</v>
       </c>
@@ -434,6 +452,9 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
